--- a/prep_and_checklists/Global Impact Social Welfare Fund  /PLATEWARE PULL SHEET Global Impact Social Welfare Fund  _Saturday, March 7, 2026  _0.xlsx
+++ b/prep_and_checklists/Global Impact Social Welfare Fund  /PLATEWARE PULL SHEET Global Impact Social Welfare Fund  _Saturday, March 7, 2026  _0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Global Impact Social Welfare Fund  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AABFD4C-132B-BC49-8412-3033EC6C9ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBF055E-50B0-514A-89C7-D117706CDD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="1140" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="300" yWindow="980" windowWidth="29940" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Updated_Pull_Sheet" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,25 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Inventory!$A$1:$E$75</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="106">
   <si>
     <t xml:space="preserve">Event: Global Impact Social Welfare Fund   Date: Saturday, March 7, 2026  </t>
   </si>
@@ -4566,8 +4579,12 @@
       <c r="A28" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="149"/>
-      <c r="C28" s="149"/>
+      <c r="B28" s="149">
+        <v>2</v>
+      </c>
+      <c r="C28" s="149" t="s">
+        <v>104</v>
+      </c>
       <c r="D28" s="126"/>
       <c r="E28" s="74" t="s">
         <v>48</v>
@@ -6262,7 +6279,7 @@
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
